--- a/candidate_pool/default_solv_candidate.xlsx
+++ b/candidate_pool/default_solv_candidate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/sh19129_bristol_ac_uk/Documents/Documents/MyProject/ML/HSP_python/calculation/cal_20221227_solv_pred_v2/hsp_toolkit_solv_pred_v_2.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/xfang1_ic_ac_uk/Documents/Documents/My_code/SolvPred/hsp_toolkit_solv_pred_v_2.0/candidate_pool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1173" documentId="11_F25DC773A252ABDACC1048E8991D7BDE5BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD02CC29-BFF5-4F0F-80CC-9AE027D3441C}"/>
+  <xr:revisionPtr revIDLastSave="1174" documentId="11_F25DC773A252ABDACC1048E8991D7BDE5BDE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{029569ED-2392-440F-8980-26E2139D014F}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mix" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>CAS</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>108-39-4</t>
+  </si>
+  <si>
+    <t>Diethylether</t>
   </si>
 </sst>
 </file>
@@ -633,7 +636,7 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -900,21 +903,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002963E37866ED33418AA3C2E7C2CBC48C" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="722427c93779db870d9b88208615f41a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3daf175e-d399-4f27-8e26-d8d48fd6e34f" xmlns:ns3="811be916-0eb4-48a2-b739-bdd7ef3c3bb9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a852b18fc1bf161a89c57f3c04037867" ns2:_="" ns3:_="">
     <xsd:import namespace="3daf175e-d399-4f27-8e26-d8d48fd6e34f"/>
@@ -1125,24 +1113,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCC6C4B-3617-4EB2-A0A6-328E290B3C20}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{440AC86F-A7D9-4E52-9514-D7770551CDF7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86B4E36-C5CD-4621-AE12-D0AE4890F71B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1159,4 +1145,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{440AC86F-A7D9-4E52-9514-D7770551CDF7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCC6C4B-3617-4EB2-A0A6-328E290B3C20}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>